--- a/results/04_final_refined_daily_hydroclimate_data/209/Dry_bulb_temp_06h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/209/Dry_bulb_temp_06h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Year</t>
   </si>
@@ -26,9 +26,6 @@
   </si>
   <si>
     <t>Dry_bulb_temp_06h00</t>
-  </si>
-  <si>
-    <t>NaN</t>
   </si>
 </sst>
 </file>
@@ -427,8 +424,8 @@
       <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
-        <v>4</v>
+      <c r="D3">
+        <v>19.1</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -455,8 +452,8 @@
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5" t="s">
-        <v>4</v>
+      <c r="D5">
+        <v>17.3</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -469,8 +466,8 @@
       <c r="C6">
         <v>5</v>
       </c>
-      <c r="D6" t="s">
-        <v>4</v>
+      <c r="D6">
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -483,8 +480,8 @@
       <c r="C7">
         <v>6</v>
       </c>
-      <c r="D7" t="s">
-        <v>4</v>
+      <c r="D7">
+        <v>20.1</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -497,8 +494,8 @@
       <c r="C8">
         <v>7</v>
       </c>
-      <c r="D8" t="s">
-        <v>4</v>
+      <c r="D8">
+        <v>20.6</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -511,8 +508,8 @@
       <c r="C9">
         <v>8</v>
       </c>
-      <c r="D9" t="s">
-        <v>4</v>
+      <c r="D9">
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -525,8 +522,8 @@
       <c r="C10">
         <v>9</v>
       </c>
-      <c r="D10" t="s">
-        <v>4</v>
+      <c r="D10">
+        <v>19.8</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -539,8 +536,8 @@
       <c r="C11">
         <v>10</v>
       </c>
-      <c r="D11" t="s">
-        <v>4</v>
+      <c r="D11">
+        <v>20.4</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -554,7 +551,7 @@
         <v>11</v>
       </c>
       <c r="D12">
-        <v>19.6</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -736,7 +733,7 @@
         <v>24</v>
       </c>
       <c r="D25">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -806,7 +803,7 @@
         <v>29</v>
       </c>
       <c r="D30">
-        <v>17.2</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="31" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/209/Dry_bulb_temp_06h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/209/Dry_bulb_temp_06h00_timeseries.xlsx
@@ -733,7 +733,7 @@
         <v>24</v>
       </c>
       <c r="D25">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -803,7 +803,7 @@
         <v>29</v>
       </c>
       <c r="D30">
-        <v>17.8</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="31" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/209/Dry_bulb_temp_06h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/209/Dry_bulb_temp_06h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -26,6 +26,9 @@
   </si>
   <si>
     <t>Dry_bulb_temp_06h00</t>
+  </si>
+  <si>
+    <t>NaN</t>
   </si>
 </sst>
 </file>
@@ -620,8 +623,8 @@
       <c r="C17">
         <v>16</v>
       </c>
-      <c r="D17">
-        <v>19.5</v>
+      <c r="D17" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -634,8 +637,8 @@
       <c r="C18">
         <v>17</v>
       </c>
-      <c r="D18">
-        <v>19</v>
+      <c r="D18" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -648,8 +651,8 @@
       <c r="C19">
         <v>18</v>
       </c>
-      <c r="D19">
-        <v>20.2</v>
+      <c r="D19" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -662,8 +665,8 @@
       <c r="C20">
         <v>19</v>
       </c>
-      <c r="D20">
-        <v>20.6</v>
+      <c r="D20" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -676,8 +679,8 @@
       <c r="C21">
         <v>20</v>
       </c>
-      <c r="D21">
-        <v>20.3</v>
+      <c r="D21" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/209/Dry_bulb_temp_06h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/209/Dry_bulb_temp_06h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Year</t>
   </si>
@@ -26,9 +26,6 @@
   </si>
   <si>
     <t>Dry_bulb_temp_06h00</t>
-  </si>
-  <si>
-    <t>NaN</t>
   </si>
 </sst>
 </file>
@@ -623,8 +620,8 @@
       <c r="C17">
         <v>16</v>
       </c>
-      <c r="D17" t="s">
-        <v>4</v>
+      <c r="D17">
+        <v>19.5</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -637,8 +634,8 @@
       <c r="C18">
         <v>17</v>
       </c>
-      <c r="D18" t="s">
-        <v>4</v>
+      <c r="D18">
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -651,8 +648,8 @@
       <c r="C19">
         <v>18</v>
       </c>
-      <c r="D19" t="s">
-        <v>4</v>
+      <c r="D19">
+        <v>20.2</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -665,8 +662,8 @@
       <c r="C20">
         <v>19</v>
       </c>
-      <c r="D20" t="s">
-        <v>4</v>
+      <c r="D20">
+        <v>20.6</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -679,8 +676,8 @@
       <c r="C21">
         <v>20</v>
       </c>
-      <c r="D21" t="s">
-        <v>4</v>
+      <c r="D21">
+        <v>20.3</v>
       </c>
     </row>
     <row r="22" spans="1:4">
